--- a/netfly_api_operation_codes.xlsx
+++ b/netfly_api_operation_codes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PRACA\NETFLY_PROJECT\Netfly_API\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a20b5cd9113ca50a/Documents/PROJECTS/NETFLY_PROJECT/Netfly_API/API_Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2DAFCB0-FD9E-4D20-91C2-F74CBD64C3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="13_ncr:1_{6445B95E-E03A-46CF-BEF6-72487E593609}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD763819-3763-4BCA-8608-7EB1184D19B4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7943EF09-5264-4388-BAF8-0B1F8CDFD68A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7943EF09-5264-4388-BAF8-0B1F8CDFD68A}"/>
   </bookViews>
   <sheets>
     <sheet name="Operation Codes" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="186">
   <si>
     <t>Explanation</t>
   </si>
@@ -416,7 +416,184 @@
     <t>PL501</t>
   </si>
   <si>
-    <t>failed to retrieve list</t>
+    <t>no webhook registered for the client</t>
+  </si>
+  <si>
+    <t>WH500</t>
+  </si>
+  <si>
+    <t>WH001</t>
+  </si>
+  <si>
+    <t>WH002</t>
+  </si>
+  <si>
+    <t>invalid 'url' parameter</t>
+  </si>
+  <si>
+    <t>missing 'url' parameter</t>
+  </si>
+  <si>
+    <t>webhook successfully created</t>
+  </si>
+  <si>
+    <t>WHC00</t>
+  </si>
+  <si>
+    <t>WHU00</t>
+  </si>
+  <si>
+    <t>webhook successfully updated</t>
+  </si>
+  <si>
+    <t>Webhook Create/Update</t>
+  </si>
+  <si>
+    <t>WHC01</t>
+  </si>
+  <si>
+    <t>failed to create the webhook</t>
+  </si>
+  <si>
+    <t>WHU01</t>
+  </si>
+  <si>
+    <t>failed to update the webhook</t>
+  </si>
+  <si>
+    <t>WH003</t>
+  </si>
+  <si>
+    <t>Webhook Get Information</t>
+  </si>
+  <si>
+    <t>WHI00</t>
+  </si>
+  <si>
+    <t>info returned to client</t>
+  </si>
+  <si>
+    <t>Webhook Delete</t>
+  </si>
+  <si>
+    <t>WHD00</t>
+  </si>
+  <si>
+    <t>webhook deleted successfully</t>
+  </si>
+  <si>
+    <t>Webhook Test</t>
+  </si>
+  <si>
+    <t>WHT00</t>
+  </si>
+  <si>
+    <t>WHT01</t>
+  </si>
+  <si>
+    <t>WHT02</t>
+  </si>
+  <si>
+    <t>failed to send test payload</t>
+  </si>
+  <si>
+    <t>missing file</t>
+  </si>
+  <si>
+    <t>unable to build payload from file</t>
+  </si>
+  <si>
+    <t>webhook test sent</t>
+  </si>
+  <si>
+    <t>WHT03</t>
+  </si>
+  <si>
+    <t>PMC09</t>
+  </si>
+  <si>
+    <t>at least one document type is required</t>
+  </si>
+  <si>
+    <t>PMC10</t>
+  </si>
+  <si>
+    <t>unknown document type(s)</t>
+  </si>
+  <si>
+    <t>PMC11</t>
+  </si>
+  <si>
+    <t>cannot retrieve Hermes migration key</t>
+  </si>
+  <si>
+    <t>PMC12</t>
+  </si>
+  <si>
+    <t>participant already exists in another SMP</t>
+  </si>
+  <si>
+    <t>PMC13</t>
+  </si>
+  <si>
+    <t>failed to create service group in SMP</t>
+  </si>
+  <si>
+    <t>failed to create service metadata for docType</t>
+  </si>
+  <si>
+    <t>PMU08</t>
+  </si>
+  <si>
+    <t>PMC08</t>
+  </si>
+  <si>
+    <t>PMU09</t>
+  </si>
+  <si>
+    <t>PMU10</t>
+  </si>
+  <si>
+    <t>PMD05</t>
+  </si>
+  <si>
+    <t>failed to delete participant from SMP</t>
+  </si>
+  <si>
+    <t>PMC14</t>
+  </si>
+  <si>
+    <t>the participant is already registered in the Netfly SMP</t>
+  </si>
+  <si>
+    <t>PMC15</t>
+  </si>
+  <si>
+    <t>participant added, but already registered in another SMP. Admin has been notified.</t>
+  </si>
+  <si>
+    <t>Accepted</t>
+  </si>
+  <si>
+    <t>PMC16</t>
+  </si>
+  <si>
+    <t>participant is already managed by another client</t>
+  </si>
+  <si>
+    <t>failed to create metadata</t>
+  </si>
+  <si>
+    <t>PMU11</t>
+  </si>
+  <si>
+    <t>failed to delete metadata</t>
+  </si>
+  <si>
+    <t>Conflict</t>
+  </si>
+  <si>
+    <t>failed to retrieve the participants list</t>
   </si>
 </sst>
 </file>
@@ -507,9 +684,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -519,15 +705,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,6 +721,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -865,7 +1047,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D79"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" customWidth="1"/>
@@ -889,12 +1071,12 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1024,12 +1206,12 @@
     </row>
     <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="7"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1215,12 +1397,12 @@
     </row>
     <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="4"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -1322,12 +1504,12 @@
     </row>
     <row r="36" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="37" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="4"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -1429,12 +1611,12 @@
     </row>
     <row r="45" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="46" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="4"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="7"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -1549,183 +1731,202 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>97</v>
-      </c>
-      <c r="B55" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55">
-        <v>500</v>
-      </c>
-      <c r="D55" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="57" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="D57" s="4"/>
+      <c r="A55" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C55" s="8">
+        <v>400</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A56" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C56" s="8">
+        <v>400</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A57" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="C57" s="8">
+        <v>500</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>111</v>
-      </c>
-      <c r="B58" t="s">
-        <v>107</v>
-      </c>
-      <c r="C58">
-        <v>200</v>
-      </c>
-      <c r="D58" t="s">
-        <v>53</v>
+      <c r="A58" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C58" s="8">
+        <v>400</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>100</v>
-      </c>
-      <c r="B59" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59">
-        <v>400</v>
-      </c>
-      <c r="D59" t="s">
-        <v>28</v>
+      <c r="A59" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C59" s="8">
+        <v>500</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>101</v>
-      </c>
-      <c r="B60" t="s">
-        <v>89</v>
-      </c>
-      <c r="C60">
-        <v>400</v>
-      </c>
-      <c r="D60" t="s">
-        <v>28</v>
+      <c r="A60" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C60" s="8">
+        <v>500</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>102</v>
-      </c>
-      <c r="B61" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61">
-        <v>400</v>
-      </c>
-      <c r="D61" t="s">
+      <c r="A61" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C61" s="8">
+        <v>400</v>
+      </c>
+      <c r="D61" s="8" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>103</v>
-      </c>
-      <c r="B62" t="s">
-        <v>93</v>
-      </c>
-      <c r="C62">
-        <v>400</v>
-      </c>
-      <c r="D62" t="s">
-        <v>28</v>
+      <c r="A62" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C62" s="8">
+        <v>202</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>104</v>
-      </c>
-      <c r="B63" t="s">
-        <v>92</v>
-      </c>
-      <c r="C63">
-        <v>400</v>
-      </c>
-      <c r="D63" t="s">
-        <v>28</v>
+      <c r="A63" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C63" s="8">
+        <v>409</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C64">
-        <v>404</v>
+        <v>500</v>
       </c>
       <c r="D64" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>112</v>
-      </c>
-      <c r="B65" t="s">
-        <v>108</v>
-      </c>
-      <c r="C65">
-        <v>500</v>
-      </c>
-      <c r="D65" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>97</v>
-      </c>
-      <c r="B66" t="s">
-        <v>66</v>
-      </c>
-      <c r="C66">
-        <v>500</v>
-      </c>
-      <c r="D66" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="68" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="7"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="66" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="7"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>111</v>
+      </c>
+      <c r="B67" t="s">
+        <v>107</v>
+      </c>
+      <c r="C67">
+        <v>200</v>
+      </c>
+      <c r="D67" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>100</v>
+      </c>
+      <c r="B68" t="s">
+        <v>85</v>
+      </c>
+      <c r="C68">
+        <v>400</v>
+      </c>
+      <c r="D68" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="C69">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="D69" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C70">
         <v>400</v>
@@ -1736,10 +1937,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>400</v>
@@ -1750,38 +1951,38 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C72">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D72" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="B73" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C73">
-        <v>500</v>
+        <v>404</v>
       </c>
       <c r="D73" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B74" t="s">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="C74">
         <v>500</v>
@@ -1790,55 +1991,552 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="77" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="7"/>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="C75" s="8">
+        <v>400</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="8">
+        <v>400</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C77" s="8">
+        <v>500</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>124</v>
-      </c>
-      <c r="B78" t="s">
-        <v>82</v>
-      </c>
-      <c r="C78">
-        <v>200</v>
-      </c>
-      <c r="D78" t="s">
-        <v>53</v>
+      <c r="A78" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" s="8">
+        <v>500</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>97</v>
+      </c>
+      <c r="B79" t="s">
+        <v>66</v>
+      </c>
+      <c r="C79">
+        <v>500</v>
+      </c>
+      <c r="D79" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="4"/>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>114</v>
+      </c>
+      <c r="B82" t="s">
+        <v>115</v>
+      </c>
+      <c r="C82">
+        <v>200</v>
+      </c>
+      <c r="D82" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>116</v>
+      </c>
+      <c r="B83" t="s">
+        <v>117</v>
+      </c>
+      <c r="C83">
+        <v>400</v>
+      </c>
+      <c r="D83" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>119</v>
+      </c>
+      <c r="B84" t="s">
+        <v>118</v>
+      </c>
+      <c r="C84">
+        <v>400</v>
+      </c>
+      <c r="D84" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>120</v>
+      </c>
+      <c r="B85" t="s">
+        <v>106</v>
+      </c>
+      <c r="C85">
+        <v>404</v>
+      </c>
+      <c r="D85" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>121</v>
+      </c>
+      <c r="B86" t="s">
+        <v>122</v>
+      </c>
+      <c r="C86">
+        <v>500</v>
+      </c>
+      <c r="D86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="8">
+        <v>500</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>97</v>
+      </c>
+      <c r="B88" t="s">
+        <v>66</v>
+      </c>
+      <c r="C88">
+        <v>500</v>
+      </c>
+      <c r="D88" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="90" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="4"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>124</v>
+      </c>
+      <c r="B91" t="s">
+        <v>82</v>
+      </c>
+      <c r="C91">
+        <v>200</v>
+      </c>
+      <c r="D91" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
         <v>125</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B92" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92">
+        <v>500</v>
+      </c>
+      <c r="D92" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="94" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="4"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>133</v>
+      </c>
+      <c r="B95" t="s">
+        <v>132</v>
+      </c>
+      <c r="C95">
+        <v>200</v>
+      </c>
+      <c r="D95" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>134</v>
+      </c>
+      <c r="B96" t="s">
+        <v>135</v>
+      </c>
+      <c r="C96">
+        <v>200</v>
+      </c>
+      <c r="D96" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>128</v>
+      </c>
+      <c r="B97" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97">
+        <v>400</v>
+      </c>
+      <c r="D97" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>129</v>
+      </c>
+      <c r="B98" t="s">
+        <v>130</v>
+      </c>
+      <c r="C98">
+        <v>400</v>
+      </c>
+      <c r="D98" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>141</v>
+      </c>
+      <c r="B99" t="s">
         <v>126</v>
       </c>
-      <c r="C79">
-        <v>500</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="C99">
+        <v>404</v>
+      </c>
+      <c r="D99" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>137</v>
+      </c>
+      <c r="B100" t="s">
+        <v>138</v>
+      </c>
+      <c r="C100">
+        <v>500</v>
+      </c>
+      <c r="D100" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>139</v>
+      </c>
+      <c r="B101" t="s">
+        <v>140</v>
+      </c>
+      <c r="C101">
+        <v>500</v>
+      </c>
+      <c r="D101" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>127</v>
+      </c>
+      <c r="B102" t="s">
+        <v>66</v>
+      </c>
+      <c r="C102">
+        <v>500</v>
+      </c>
+      <c r="D102" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="104" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="4"/>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>143</v>
+      </c>
+      <c r="B105" t="s">
+        <v>144</v>
+      </c>
+      <c r="C105">
+        <v>200</v>
+      </c>
+      <c r="D105" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>141</v>
+      </c>
+      <c r="B106" t="s">
+        <v>126</v>
+      </c>
+      <c r="C106">
+        <v>404</v>
+      </c>
+      <c r="D106" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>127</v>
+      </c>
+      <c r="B107" t="s">
+        <v>66</v>
+      </c>
+      <c r="C107">
+        <v>500</v>
+      </c>
+      <c r="D107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="109" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A109" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="4"/>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>146</v>
+      </c>
+      <c r="B110" t="s">
+        <v>147</v>
+      </c>
+      <c r="C110">
+        <v>200</v>
+      </c>
+      <c r="D110" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>141</v>
+      </c>
+      <c r="B111" t="s">
+        <v>126</v>
+      </c>
+      <c r="C111">
+        <v>404</v>
+      </c>
+      <c r="D111" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>127</v>
+      </c>
+      <c r="B112" t="s">
+        <v>66</v>
+      </c>
+      <c r="C112">
+        <v>500</v>
+      </c>
+      <c r="D112" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="114" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A114" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="4"/>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>149</v>
+      </c>
+      <c r="B115" t="s">
+        <v>155</v>
+      </c>
+      <c r="C115">
+        <v>200</v>
+      </c>
+      <c r="D115" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>150</v>
+      </c>
+      <c r="B116" t="s">
+        <v>153</v>
+      </c>
+      <c r="C116">
+        <v>400</v>
+      </c>
+      <c r="D116" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>151</v>
+      </c>
+      <c r="B117" t="s">
+        <v>154</v>
+      </c>
+      <c r="C117">
+        <v>500</v>
+      </c>
+      <c r="D117" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>156</v>
+      </c>
+      <c r="B118" t="s">
+        <v>152</v>
+      </c>
+      <c r="C118">
+        <v>500</v>
+      </c>
+      <c r="D118" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>141</v>
+      </c>
+      <c r="B119" t="s">
+        <v>126</v>
+      </c>
+      <c r="C119">
+        <v>404</v>
+      </c>
+      <c r="D119" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" t="s">
+        <v>66</v>
+      </c>
+      <c r="C120">
+        <v>500</v>
+      </c>
+      <c r="D120" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A77:D77"/>
+  <mergeCells count="12">
+    <mergeCell ref="A114:D114"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A28:D28"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A90:D90"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="94" fitToHeight="0" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>